--- a/education_surveys/010_education_policy_awareness_survey--education_surveys.xlsx
+++ b/education_surveys/010_education_policy_awareness_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'fully_understand'}</t>
+          <t>fully_understand</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Fully understand'}</t>
+          <t>Fully understand</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_understand'}</t>
+          <t>somewhat_understand</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat understand'}</t>
+          <t>Somewhat understand</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_"don't_understand"}</t>
+          <t>don't_understand</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': "Don't understand"}</t>
+          <t>Don't understand</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'positive_impact'}</t>
+          <t>positive_impact</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Positive Impact'}</t>
+          <t>Positive Impact</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'negative_impact'}</t>
+          <t>negative_impact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Negative Impact'}</t>
+          <t>Negative Impact</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'neutral_impact'}</t>
+          <t>neutral_impact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral Impact'}</t>
+          <t>Neutral Impact</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_support'}</t>
+          <t>strongly_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Support'}</t>
+          <t>Strongly Support</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_support'}</t>
+          <t>somewhat_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Support'}</t>
+          <t>Somewhat Support</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_influential'}</t>
+          <t>very_influential</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Influential'}</t>
+          <t>Very Influential</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_influential'}</t>
+          <t>somewhat_influential</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Influential'}</t>
+          <t>Somewhat Influential</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_influential'}</t>
+          <t>not_influential</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not Influential'}</t>
+          <t>Not Influential</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'very_effective'}</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Very Effective'}</t>
+          <t>Very Effective</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Effective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not Effective'}</t>
+          <t>Not Effective</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'very_sustainable'}</t>
+          <t>very_sustainable</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Very Sustainable'}</t>
+          <t>Very Sustainable</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_sustainable'}</t>
+          <t>somewhat_sustainable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Sustainable'}</t>
+          <t>Somewhat Sustainable</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_sustainable'}</t>
+          <t>not_sustainable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sustainable'}</t>
+          <t>Not Sustainable</t>
         </is>
       </c>
     </row>
